--- a/public/database/SMW/SMW/SMW.xlsx
+++ b/public/database/SMW/SMW/SMW.xlsx
@@ -496,10 +496,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Hello! As a premium PTE teacher, I can guide you through the strategic thinking required for the Select Missing Word question type. This section tests not only your listening skills but also your ability to understand the semantic and grammatical flow of an academic passage. Here is a detailed breakdown of the correct answer and the incorrect distractors.&lt;/p&gt;
-&lt;h3&gt;🧠 PTE Skill Focus: Contextual Completion&lt;/h3&gt;
-&lt;p&gt;In this type of question, you must imagine the missing word and make sure it connects seamlessly to the preceding and succeeding parts of the conversation. The topic is the history of banking, so the missing word must relate to financial instruments or banking terminology.&lt;/p&gt;
-&lt;h4&gt;✅ Analysis of the Correct Option: notes&lt;/h4&gt;
+          <t>&lt;h4&gt;✅ Analysis of the Correct Option: notes&lt;/h4&gt;
 &lt;ul&gt;
 &lt;li&gt;&lt;b&gt;Contextual Fit:&lt;/b&gt; The passage is discussing various forms of paper money, financial documents (bills of exchange), and the evolution of banking. When talking about a "proper European bank," the primary physical output or guarantee of the bank is the money it issues—which are &lt;b&gt;bank notes&lt;/b&gt;.&lt;/li&gt;
 &lt;li&gt;&lt;b&gt;Grammatical Fit:&lt;/b&gt; The sentence structure is: "However, it is the Swedes who are generally credited with producing the first proper European bank &lt;b&gt;notes&lt;/b&gt;." The word "notes" functions as the primary noun object, completing the thought initiated by "bank." It suggests the production of currency or documented financial notes.&lt;/li&gt;
@@ -544,9 +541,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;🧠 Premium PTE Analysis: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;This is a high-level vocabulary and contextual inference question. To answer correctly, you must not only understand the grammar of the sentence but also grasp the overarching tone and point of conflict established by the speaker.&lt;/p&gt;
-&lt;h4&gt;✅ Analysis of the Correct Option: "could very possibly be fake"&lt;/h4&gt;
+          <t>&lt;h4&gt;✅ Analysis of the Correct Option: "could very possibly be fake"&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;1. Contextual Fit (Tone):&lt;/strong&gt; The passage establishes a pattern of positive information ("exciting find," "reveal much") followed by a clear counterpoint signaled by the transitional phrase &lt;strong&gt;"However"&lt;/strong&gt;. The speaker states, "many scholars are &lt;strong&gt;sceptical about the authenticity&lt;/strong&gt; of the blocks." The word "authenticity" means the state of being genuine or real. The only phrase that logically completes the thought of academic skepticism regarding genuineness is suggesting that the items might not be real. "Could very possibly be fake" directly reinforces and explains the scholars' skepticism.&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;2. Grammatical Fit:&lt;/strong&gt; The structure is: "...blocks, which they suspect [BEEP]." The relative pronoun "which" refers to the "blocks." The phrase "could very possibly be fake" functions perfectly as a predicative adjective clause, describing the blocks' potential state (their suspected nature).&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; The suspicion of scholars (doubt) logically leads directly to the conclusion that the objects might not be genuine (fake). This option completes the scholarly critique of the find.&lt;/p&gt;
@@ -588,9 +583,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;🌟 PTE Listening Strategy: Select Missing Word (Contextual Vocabulary)&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;In this question type, you must use your understanding of context and vocabulary to select the word that logically and grammatically completes the passage. The core principle is matching the meaning (semantics) of the surrounding text to the given choices.&lt;/p&gt;
-&lt;h3&gt;✅ Analysis of the Correct Option: Complex&lt;/h3&gt;
+          <t>&lt;h3&gt;✅ Analysis of the Correct Option: Complex&lt;/h3&gt;
 &lt;p&gt;&lt;strong&gt;The Context:&lt;/strong&gt; The speaker is describing the viewing experience of a leaf under a microscope. They use phrases like "amazing detail," "suddenly huge," and "amazingly intricate." The overall tone is one of profound realization about the object's sophisticated structure.&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Why 'Complex' Works:&lt;/strong&gt;
 &lt;ul&gt;
@@ -640,8 +633,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;🌟 PTE Listening Deep Dive: Select Missing Word&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question tests not only your listening comprehension but also your ability to grasp the academic context and determine the most appropriate lexical fit (grammar and meaning) for a concluding statement. In this passage, the speaker is adopting a tone of measured advice, suggesting that while dreams are important, they must be grounded in reality.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests not only your listening comprehension but also your ability to grasp the academic context and determine the most appropriate lexical fit (grammar and meaning) for a concluding statement. In this passage, the speaker is adopting a tone of measured advice, suggesting that while dreams are important, they must be grounded in reality.&lt;/p&gt;
 &lt;h4&gt;✅ Analysis of the Correct Option: &lt;strong&gt;realistic&lt;/strong&gt;&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it is correct:&lt;/strong&gt;&lt;/p&gt;
 &lt;ol&gt;
@@ -792,8 +784,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;🌟 PTE Listening Strategy: Select Missing Word Analysis&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question requires you to identify the phrase that maintains the &lt;strong&gt;contextual and chronological&lt;/strong&gt; flow of the narrative. The key is understanding that the sentence establishes a span of time, moving from a distant past to a more recent endpoint.&lt;/p&gt;
+          <t>&lt;p&gt;This question requires you to identify the phrase that maintains the &lt;strong&gt;contextual and chronological&lt;/strong&gt; flow of the narrative. The key is understanding that the sentence establishes a span of time, moving from a distant past to a more recent endpoint.&lt;/p&gt;
 &lt;h4&gt;✅ Analysis of the Correct Option: &lt;strong&gt;current days&lt;/strong&gt;&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Function:&lt;/strong&gt; The sentence establishes a time continuum: "from early humanity to [BEEP]". The correct answer, &lt;strong&gt;current days&lt;/strong&gt;, perfectly completes this timeline.&lt;/p&gt;
 &lt;ul&gt;
@@ -852,8 +843,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;📝 PTE Listening: Select Missing Word Analysis&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question tests your ability to understand the overall academic argument and identify the word that completes the logical flow and maintains grammatical consistency in the comparative statement.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to understand the overall academic argument and identify the word that completes the logical flow and maintains grammatical consistency in the comparative statement.&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Context Summary:&lt;/strong&gt; The speaker is contrasting two types of children: those whose parents use physical punishment (negative outcomes) versus those whose parents use less harsh discipline (positive outcomes). The missing word must complete the list of positive effects observed in the first group.&lt;/p&gt;
 &lt;h4&gt;✅ The Correct Option: Peers&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it is correct:&lt;/strong&gt;&lt;br&gt;The structure of the sentence builds a comprehensive description of the positive effects of non-punitive parenting. The phrase, "healthier attitude towards their school environment and &lt;strong&gt;peers&lt;/strong&gt;," is highly logical.&lt;br&gt;&lt;br&gt;&lt;strong&gt;1. Contextual Fit:&lt;/strong&gt; When discussing a child's attitude in a "school environment," the key relationships are the school itself (the environment) and the people they interact with regularly (the peers/classmates). This choice maintains the focus on the social and educational sphere.&lt;br&gt;&lt;strong&gt;2. Grammatical Consistency:&lt;/strong&gt; "Peers" is a simple plural noun that fits perfectly into the correlative structure established by "attitude towards..." It completes the idea that the children are adjusting well not only to the school structure but also to their classmates.&lt;/p&gt;
@@ -895,8 +885,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;🎧 PTE Listening: Select Missing Word Analysis&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question tests your ability to understand the *contextual flow* and *grammatical structure* of a passage. The missing phrase must act as the logical conclusion to the statement, explaining the primary motivation for the discreet design of the "detective cameras."&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to understand the *contextual flow* and *grammatical structure* of a passage. The missing phrase must act as the logical conclusion to the statement, explaining the primary motivation for the discreet design of the "detective cameras."&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option Analysis: "as they took pictures"&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it works:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
@@ -987,8 +976,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;📝 Detailed Analysis: Select Missing Word (Listening)&lt;/h3&gt;
-&lt;p&gt;This question requires you to listen for context clues. The speaker provides a reason for changing the assessment format. The correct option must logically explain *why* the change is necessary, filling the gap in the speaker's argument.&lt;/p&gt;
+          <t>&lt;p&gt;This question requires you to listen for context clues. The speaker provides a reason for changing the assessment format. The correct option must logically explain *why* the change is necessary, filling the gap in the speaker's argument.&lt;/p&gt;
 &lt;h4&gt;✅ Analysis of the Correct Option&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;The correct choice is: &lt;em&gt;they made an inappropriate choice of topic&lt;/em&gt;.&lt;/strong&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Contextual Fit:&lt;/strong&gt;&lt;/p&gt;
@@ -1037,8 +1025,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;⭐ PTE Analysis: Select Missing Word (Listening)&lt;/h3&gt;
-&lt;p&gt;This question tests not only your listening comprehension but also your ability to maintain &lt;strong&gt;coherence&lt;/strong&gt; and &lt;em&gt;contextual fit&lt;/em&gt;. The speaker is building a specific argument: General education (humanities) is valuable because it makes you better at problem-solving.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests not only your listening comprehension but also your ability to maintain &lt;strong&gt;coherence&lt;/strong&gt; and &lt;em&gt;contextual fit&lt;/em&gt;. The speaker is building a specific argument: General education (humanities) is valuable because it makes you better at problem-solving.&lt;/p&gt;
 &lt;h4&gt;🧠 Context Analysis&lt;/h4&gt;
 &lt;p&gt;The critical sentence leading up to the beep is: "This broad education means they can approach an issue [BEEP]."
 &lt;br&gt;
@@ -1095,8 +1082,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Hello! As your premium PTE Academic teacher, let's break down this challenging Listening task. The &lt;strong&gt;Select Missing Word&lt;/strong&gt; question tests not only your listening comprehension but also your ability to analyze grammar and context simultaneously. This specific question requires understanding an idiomatic phrase.&lt;/p&gt;
-&lt;h3&gt;✅ Analysis of the Correct Option: &lt;em&gt;were at stake&lt;/em&gt;&lt;/h3&gt;
+          <t>&lt;h3&gt;✅ Analysis of the Correct Option: &lt;em&gt;were at stake&lt;/em&gt;&lt;/h3&gt;
 &lt;p&gt;&lt;strong&gt;Why it is correct:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
     &lt;li&gt;&lt;strong&gt;Contextual Fit:&lt;/strong&gt; The passage describes fierce, high-stakes competitions. The phrase &lt;em&gt;"at stake"&lt;/em&gt; is an idiom that means "at risk," "of concern," or "something that could be lost." When discussing competitions involving emotion, status, or resources (like wealth, pride, and romance), it is natural to state that these things &lt;strong&gt;were at stake&lt;/strong&gt;.&lt;/li&gt;
@@ -1201,8 +1187,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Welcome! As a premium PTE Academic teacher, I will guide you through the precise grammatical, contextual, and logical reasoning needed to select the best missing word. This process requires you to consider the &lt;strong&gt;overall tone&lt;/strong&gt; and the &lt;strong&gt;climax&lt;/strong&gt; of the speaker’s argument.&lt;/p&gt;
-&lt;h3&gt;🎯 Strategy: Identifying the Conceptual Flow&lt;/h3&gt;
+          <t>&lt;h3&gt;🎯 Strategy: Identifying the Conceptual Flow&lt;/h3&gt;
 &lt;p&gt;In a 'Select Missing Word' question, the best answer must not only be grammatically correct but must also serve as the &lt;em&gt;logical culmination&lt;/em&gt; of the preceding sentences. The speaker has spent time establishing that touch is a highly sophisticated and complex sense. The final statement must summarize this complexity in terms of current scientific knowledge.&lt;/p&gt;
 &lt;h3&gt;✅ Analysis of the Correct Option&lt;/h3&gt;
 &lt;h4&gt;&lt;b&gt;still poorly understood&lt;/b&gt;&lt;/h4&gt;
@@ -1250,8 +1235,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;⭐ PTE Listening Strategy: Select Missing Word Analysis&lt;/h3&gt;
-&lt;p&gt;This question tests not only your listening comprehension but also your ability to understand the speaker's overarching narrative structure and identify the most logically consistent completion. In a "Select Missing Word" task, the missing phrase must serve a perfect grammatical and contextual purpose at the end of the sentence.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests not only your listening comprehension but also your ability to understand the speaker's overarching narrative structure and identify the most logically consistent completion. In a "Select Missing Word" task, the missing phrase must serve a perfect grammatical and contextual purpose at the end of the sentence.&lt;/p&gt;
 &lt;h4&gt;📚 Contextual Analysis&lt;/h4&gt;
 &lt;p&gt;The speaker is giving academic research advice. The final paragraph advises checking "references shelves and newspaper section." The transition word used is &lt;strong&gt;"though a problem here is finding..."&lt;/strong&gt;. This structure signals a limitation or difficulty associated with the previous topic (references/newspapers).&lt;/p&gt;
 &lt;h4&gt;✅ Analysis of the Correct Option&lt;/h4&gt;
@@ -1302,8 +1286,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As a premium PTE Academic teacher, I understand that Select Missing Word questions test not only your listening comprehension but also your ability to understand the &lt;em&gt;speaker's tone&lt;/em&gt; and the &lt;strong&gt;semantic context&lt;/strong&gt; of the conversation. The missing word must logically conclude the speaker's current line of thought.&lt;/p&gt;
-&lt;h3&gt;&lt;h4&gt;🔍 Contextual Analysis of the Transcript&lt;/h4&gt;&lt;/h3&gt;
+          <t>&lt;h3&gt;&lt;h4&gt;🔍 Contextual Analysis of the Transcript&lt;/h4&gt;&lt;/h3&gt;
 &lt;p&gt;The speaker is describing &lt;strong&gt;road rage&lt;/strong&gt;. The tone throughout the passage is increasingly concerned, alarming, and judgmental. The speaker moves from general annoyance to describing physical violence ("They can punch the other diver and sometimes even kill them"). The final rhetorical question, "Why would you want to kill someone because they overtook you?", forces the listener to contemplate the extreme irrationality of the behavior just detailed.&lt;/p&gt;
 &lt;p&gt;The missing word must therefore be an adjective that describes this behavior as fundamentally &lt;strong&gt;illogical or insane&lt;/strong&gt;.&lt;/p&gt;
 &lt;h3&gt;&lt;h4&gt;✅ Analysis of the Correct Choice: Crazy&lt;/h4&gt;&lt;/h3&gt;
@@ -1350,8 +1333,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;🌟 PTE Listening Strategy: Select Missing Word Analysis 🌟&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question tests not only your listening comprehension but also your ability to analyze the grammatical structure and the thematic flow (coherence) of the discourse. You must choose the option that completes the list of concepts naturally and accurately.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests not only your listening comprehension but also your ability to analyze the grammatical structure and the thematic flow (coherence) of the discourse. You must choose the option that completes the list of concepts naturally and accurately.&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option Analysis: mysteries&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Rationale:&lt;/strong&gt; The sentence structure established is a list of three abstract nouns: "hidden secrets, history and [BEEP]."&lt;/p&gt;
 &lt;ul&gt;
@@ -1408,8 +1390,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;PTE Listening Strategy: Selecting Missing Concepts&lt;/h3&gt;
-&lt;p&gt;This question requires you not just to listen for a specific word, but to synthesize the overall theme and central conflict presented in the passage. The missing words must provide a conclusion or a necessary balance point that encompasses all the topics the speaker has discussed.&lt;/p&gt;
+          <t>&lt;p&gt;This question requires you not just to listen for a specific word, but to synthesize the overall theme and central conflict presented in the passage. The missing words must provide a conclusion or a necessary balance point that encompasses all the topics the speaker has discussed.&lt;/p&gt;
 &lt;h4&gt;🎯 Correct Choice Analysis: Studying and partying&lt;/h4&gt;
 &lt;p&gt;This option is the best fit because it summarizes the two major, contrasting aspects of university life that the speaker has spent the entire passage describing. The speaker establishes a balance between two distinct spheres of activity:&lt;/p&gt;
 &lt;ol&gt;
@@ -1455,8 +1436,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>&lt;p&gt;📚 PTE Teaching Analysis: Select Missing Word&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Question Type:&lt;/strong&gt; Select Missing Word (Listening)&lt;/p&gt;
+          <t>&lt;p&gt;&lt;strong&gt;Question Type:&lt;/strong&gt; Select Missing Word (Listening)&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Overall Strategy:&lt;/strong&gt; In this type of question, you must use the entire passage—not just the sentence before the beep—to predict the overall theme and the natural conclusion. The missing phrase must maintain both the grammatical flow and the thematic continuity established by the speaker.&lt;/p&gt;
 &lt;h3&gt;✔️ Analysis of the Correct Option&lt;/h3&gt;
 &lt;h4&gt;&lt;p&gt;&lt;strong&gt;Correct Choice: quality of life&lt;/strong&gt;&lt;/p&gt;&lt;/h4&gt;
@@ -1558,8 +1538,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As a premium PTE teacher, I recommend paying close attention to the overarching theme, tone, and semantic flow of the passage. In a "Select Missing Word" question, the correct answer must complete the sentence not just grammatically, but also logically and contextually based on the preceding discussion.&lt;/p&gt;
-&lt;h3&gt;✅ Analysis of the Correct Option: Coal&lt;/h3&gt;
+          <t>&lt;h3&gt;✅ Analysis of the Correct Option: Coal&lt;/h3&gt;
 &lt;p&gt;The choice &lt;strong&gt;coal&lt;/strong&gt; is the correct answer because it maintains absolute contextual coherence with the entire passage. The speaker is discussing environmental crises, specifically the damage to the ozone layer, which is linked to pollution and global warming. The sentence structure is:&lt;/p&gt;
 &lt;p&gt;&lt;em&gt;"We all need to stop driving cars and stop using [BEEP]"&lt;/em&gt;&lt;/p&gt;
 &lt;p&gt;&lt;ul&gt;
@@ -1606,9 +1585,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;🔬 PTE Listening Analysis: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;Hello! As a premium PTE Academic instructor, I can guide you through the logic and contextual clues used in this specific question type. In "Select Missing Word," you must pay close attention not just to *what* the speaker says, but the *emotion* and *direction* of the conversation. This final question is a subtle, reflective observation.&lt;/p&gt;
-&lt;h4&gt;⭐ The Correct Answer: bored&lt;/h4&gt;
+          <t>&lt;h4&gt;⭐ The Correct Answer: bored&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Contextual Fit:&lt;/strong&gt; The speaker has spent the entire passage describing the depth and complexity of child psychology (analyzing behaviors, understanding minds). The final sentence describes the job: "listening to people talk all day and then analyzing their behavior." This process sounds mentally demanding but potentially repetitive or draining. The transition from describing the analytical nature of the job to a reflective, skeptical question often points toward the potential negative side effect of that job. Therefore, asking if they "ever get bored" is the most natural and contextually appropriate conclusion to the thought.&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Grammatical Fit:&lt;/strong&gt; The structure "I wonder if they ever get [BLANK]" requires a state-of-being adjective. "Bored" fits perfectly after the phrasal verb "get," forming the idiomatic question: "I wonder if they ever get bored."&lt;/p&gt;
 &lt;h4&gt;❌ Why the Other Options Are Incorrect&lt;/h4&gt;
@@ -1652,8 +1629,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;🎯 Premium PTE Listening Analysis: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;This question tests your ability to understand the speaker's overall argument, tone, and conversational trajectory. The speaker is highly skeptical about anti-aging products, arguing that they are a waste of money. The missing phrase must serve as a powerful conclusion, summarizing the speaker's alternative view—that natural wellness, not expensive creams, is the answer.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to understand the speaker's overall argument, tone, and conversational trajectory. The speaker is highly skeptical about anti-aging products, arguing that they are a waste of money. The missing phrase must serve as a powerful conclusion, summarizing the speaker's alternative view—that natural wellness, not expensive creams, is the answer.&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option: looking younger&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it works:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
@@ -1804,8 +1780,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;🧠 PTE Teacher Analysis: Select Missing Word (Listening)&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question requires you to listen for a specific defining phrase that completes the academic concept being presented in the transcript. The core task is to understand the relationship between the concepts mentioned (Population, Sample, Characteristics) and select the option that makes the definition grammatically perfect and contextually precise.&lt;/p&gt;
+          <t>&lt;p&gt;This question requires you to listen for a specific defining phrase that completes the academic concept being presented in the transcript. The core task is to understand the relationship between the concepts mentioned (Population, Sample, Characteristics) and select the option that makes the definition grammatically perfect and contextually precise.&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option Analysis: of the population&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it is correct:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
@@ -1905,8 +1880,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>&lt;p&gt;🎯 PTE Listening Strategy: Select Missing Word Analysis&lt;/p&gt;
-&lt;p&gt;This question tests your ability to comprehend the speaker's overall argument and fill the linguistic gap with the most contextually appropriate word, even when the grammar of all options might seem plausible. Pay close attention to the speaker's tone and the underlying theme of identity.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to comprehend the speaker's overall argument and fill the linguistic gap with the most contextually appropriate word, even when the grammar of all options might seem plausible. Pay close attention to the speaker's tone and the underlying theme of identity.&lt;/p&gt;
 &lt;h3&gt;🎧 Transcript Context Analysis&lt;/h3&gt;
 &lt;p&gt;The speaker is discussing the idea that young people are often viewed as a "problem." The key preceding sentence is: "For one thing, being a problem gives you a certain identity, and that is one of the things the young are busily engaged in [BEEP]."&lt;/p&gt;
 &lt;p&gt;The speaker has established that having an identity—even one labeled negatively—is something the young are actively pursuing or doing. Therefore, the missing word must represent an active, deep, and purposeful activity related to the search for self or belonging.&lt;/p&gt;
@@ -1961,8 +1935,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>&lt;p&gt;🔬 PTE Listening Analysis: Select Missing Word&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Overall Context:&lt;/strong&gt; This passage discusses the importance of honesty, vulnerability, and acknowledging truth in parent-child relationships. The speaker suggests that while extremes exist, adopting an honest and open approach is always beneficial.&lt;/p&gt;
+          <t>&lt;p&gt;&lt;strong&gt;Overall Context:&lt;/strong&gt; This passage discusses the importance of honesty, vulnerability, and acknowledging truth in parent-child relationships. The speaker suggests that while extremes exist, adopting an honest and open approach is always beneficial.&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;The Key Phrase:&lt;/strong&gt; The final sentence is, "It is always wiser and safer to face up [BEEP]." The missing word completes a phrasal verb that dictates the concluding lesson of the passage.&lt;/p&gt;
 &lt;h3&gt;✅ Correct Option Analysis: to reality&lt;/h3&gt;
 &lt;p&gt;&lt;strong&gt;Grammar and Phrasal Verbs:&lt;/strong&gt; The phrase &lt;strong&gt;"face up to"&lt;/strong&gt; is a standard and essential phrasal verb. It means to confront, acknowledge, or accept a difficult situation or truth. In this case, the speaker advises facing the truth or the difficult facts of life, which is "reality."&lt;/p&gt;
@@ -2002,8 +1975,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;🎧 PTE Listening: Select Missing Word Analysis&lt;/h3&gt;
-&lt;p&gt;This question tests your ability to maintain contextual coherence and grammatical agreement, even when the key information is missing. The preceding context establishes a cycle of disaster, control, and eventual failure (resistance).&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to maintain contextual coherence and grammatical agreement, even when the key information is missing. The preceding context establishes a cycle of disaster, control, and eventual failure (resistance).&lt;/p&gt;
 &lt;h4&gt;⭐ The Correct Choice: Manageable&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Reasoning:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
@@ -2156,8 +2128,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Hello! As your PTE Academic teacher, I can provide a detailed breakdown of this challenging Listening task. Missing Word questions require not just good listening, but also strong understanding of context, academic vocabulary, and grammar to choose the most logical completion.&lt;/p&gt;
-&lt;h3&gt;&lt;h3&gt;🎯 Analysis of the Missing Word&lt;/h3&gt;&lt;/h3&gt;
+          <t>&lt;h3&gt;&lt;h3&gt;🎯 Analysis of the Missing Word&lt;/h3&gt;&lt;/h3&gt;
 &lt;p&gt;The segment is highly academic, discussing the biological mechanism behind the placebo effect. The crucial words preceding the gap are: &lt;em&gt;"We now think a neural chemical component, what may actually happen is the placebo effect allow some people to sort of tap into the supply of endorphins..."&lt;/em&gt;&lt;/p&gt;
 &lt;p&gt;The speaker has established that endorphins are natural, &lt;strong&gt;neural&lt;/strong&gt; chemicals. The correct answer must therefore name a source that is both a believable location for brain chemistry and structurally sound with the preceding sentence.&lt;/p&gt;
 &lt;h3&gt;&lt;h4&gt;✅ Correct Option: in their own brains&lt;/h4&gt;&lt;/h3&gt;
@@ -2338,8 +2309,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;PTE Listening Analysis: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;This question tests your ability to understand the overarching academic structure and logical flow of a lecture. When encountering a missing word following a list or a concluding generalization, you must identify the category that best completes the academic pattern established by the speaker.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to understand the overarching academic structure and logical flow of a lecture. When encountering a missing word following a list or a concluding generalization, you must identify the category that best completes the academic pattern established by the speaker.&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option: Humanities&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it is correct:&lt;/strong&gt;&lt;/p&gt;
 &lt;p&gt;The speaker is outlining the complex interdisciplinary nature of biology. The passage establishes a pattern of linking biology to various established academic fields:&lt;/p&gt;
@@ -2389,8 +2359,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;🔬 PTE Listening Mastery: Analysis of Select Missing Word&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question tests your ability to understand the overall context and logical flow of the passage, even when key information is missing. In a "Select Missing Word" type, the correct answer must not only fit grammatically but also complete the &lt;em&gt;semantic arc&lt;/em&gt; of the entire recording.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to understand the overall context and logical flow of the passage, even when key information is missing. In a "Select Missing Word" type, the correct answer must not only fit grammatically but also complete the &lt;em&gt;semantic arc&lt;/em&gt; of the entire recording.&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option Analysis: Discovery&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Choice: discovery&lt;/strong&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Rationale:&lt;/strong&gt; This option is the perfect fit both grammatically and contextually. The passage has established that science is driven by curiosity, and scientists are defined as "explorers." The natural passion of an explorer is the pursuit of new knowledge or new finds. Using "discovery" completes the logical thought: "Scientists are explorers who are passionate about &lt;strong&gt;discovery&lt;/strong&gt;." It summarizes the entire purpose of scientific inquiry—the act of finding what is unknown.&lt;/p&gt;
@@ -2436,8 +2405,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;🎧 PTE Teacher Analysis: Select Missing Word (Listening)&lt;/h3&gt;
-&lt;p&gt;This is a key vocabulary and context comprehension question. When tackling these, you must not only understand the overall narrative flow but also pay attention to the specific keywords (synonyms, genre names, academic terms) used in the preceding sentence structure. The missing word must grammatically and semantically complete the final thought.&lt;/p&gt;
+          <t>&lt;p&gt;This is a key vocabulary and context comprehension question. When tackling these, you must not only understand the overall narrative flow but also pay attention to the specific keywords (synonyms, genre names, academic terms) used in the preceding sentence structure. The missing word must grammatically and semantically complete the final thought.&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option Analysis: classical music&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it works:&lt;/strong&gt; The passage meticulously builds a historical narrative about Jazz, emphasizing its origins and its unique blend of influences. The key descriptive phrase in the sentence is: "Jazz blending African American folk roots with elements of popular music and European &lt;strong&gt;classical traditions&lt;/strong&gt;..."&lt;/p&gt;
 &lt;ul&gt;
@@ -2530,8 +2498,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Hello! Welcome to your PTE academic mastery session. This question tests not just your listening comprehension, but also your ability to deduce the most logical and contextually appropriate word. Understanding the material science and context of the passage is key here.&lt;/p&gt;
-&lt;h3&gt;💡 Detailed Analysis of the Missing Word&lt;/h3&gt;
+          <t>&lt;h3&gt;💡 Detailed Analysis of the Missing Word&lt;/h3&gt;
 &lt;p&gt;The passage is discussing the craftsmanship and construction materials used for various types of drums. The final sentence establishes that a "simple frame" needs a material to hold the membranes. We must choose the word that best fits the context of traditional, handcrafted musical instruments.&lt;/p&gt;
 &lt;h4&gt;✅ The Correct Option: Wood&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it is correct:&lt;/strong&gt;&lt;/p&gt;
@@ -2580,8 +2547,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;🔍 PTE Listening Analysis: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;This question tests not only your listening comprehension but also your ability to understand the &lt;strong&gt;semantic&lt;/strong&gt; and &lt;em&gt;contextual flow&lt;/em&gt; of the speaker. When faced with a missing word, you must select the option that completes the sentence both grammatically and scientifically (in this case, regarding cave ecology).&lt;/p&gt;
+          <t>&lt;p&gt;This question tests not only your listening comprehension but also your ability to understand the &lt;strong&gt;semantic&lt;/strong&gt; and &lt;em&gt;contextual flow&lt;/em&gt; of the speaker. When faced with a missing word, you must select the option that completes the sentence both grammatically and scientifically (in this case, regarding cave ecology).&lt;/p&gt;
 &lt;h4&gt;✅ The Correct Choice: in temperature&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Reasoning:&lt;/strong&gt; The passage is detailing the three geological and environmental zones of a cave, concluding with the description of the "Dark Zone." The speaker emphasizes that this zone is perpetually dark and stable. In scientific discussions about deep cave environments, the most significant and stable characteristic is the &lt;strong&gt;temperature&lt;/strong&gt;. Deep underground zones maintain remarkable thermal stability year-round, meaning the seasonal changes are indeed minimal. The phrase "slight seasonal changes in temperature" is a scientifically accurate and highly cohesive phrase that perfectly concludes the thought regarding the physical environment of the Dark Zone.&lt;/p&gt;
 &lt;p&gt;&lt;em&gt;Grammar and Context:&lt;/em&gt; The structure requires a measurable physical variable following "changes in." Temperature fits this requirement perfectly, making the passage logically consistent.&lt;/p&gt;
@@ -2896,8 +2862,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As a premium PTE instructor, I will guide you through the logical flow and contextual clues necessary to solve this Select Missing Word question. In this type of question, understanding the scientific context and the grammar of the cause-and-effect relationship is crucial.&lt;/p&gt;
-&lt;h3&gt;🔍 Contextual Analysis (The Clue)&lt;/h3&gt;
+          <t>&lt;h3&gt;🔍 Contextual Analysis (The Clue)&lt;/h3&gt;
 &lt;p&gt;The passage is discussing the anatomy and defensive mechanisms of the worker bee. The key sentence is: &lt;em&gt;"The worker uses her sting only once for self defense and for the protection of their colony. The worker uses her sting only once for in doing so she [BEEP]"&lt;/em&gt;&lt;/p&gt;
 &lt;p&gt;The phrase &lt;strong&gt;"in doing so"&lt;/strong&gt; establishes a direct cause-and-effect relationship. The action (using the sting) leads to the consequence (what happens to the worker). This consequence must be a profound and permanent result of the sting.&lt;/p&gt;
 &lt;h3&gt;✅ Correct Option Analysis: loses her life&lt;/h3&gt;
@@ -2946,8 +2911,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Hello! As a PTE Academic teacher, I will provide a detailed analysis of this "Select Missing Word" question. This skill tests not only your vocabulary but also your ability to understand the precise context and grammatical flow of the passage.&lt;/p&gt;
-&lt;h3&gt;🔍 Contextual Analysis: Understanding the Gap&lt;/h3&gt;
+          <t>&lt;h3&gt;🔍 Contextual Analysis: Understanding the Gap&lt;/h3&gt;
 &lt;p&gt;The passage is discussing the historical aspects of bread making. The final sentence builds suspense by describing how each household marked its loaves: "Each household would make a distinctive mark on the bread, sometimes with a special stamp bearing the family &lt;strong&gt;[BEEP]&lt;/strong&gt;."&lt;/p&gt;
 &lt;p&gt;We need a noun that serves as the primary identifier placed on a stamp (or seal) that represents a family.&lt;/p&gt;
 &lt;h3&gt;✅ Analysis of the Correct Option: Name&lt;/h3&gt;
@@ -3009,8 +2973,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;🌟 PTE Listening Deep Dive: Select Missing Word Analysis&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question tests your ability to infer the missing context, even when the direct word is replaced by a beep. The key is understanding the logical flow and the relationship between the concepts presented in the surrounding text.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to infer the missing context, even when the direct word is replaced by a beep. The key is understanding the logical flow and the relationship between the concepts presented in the surrounding text.&lt;/p&gt;
 &lt;h4&gt;🎯 1. Analysis of the Correct Choice: &lt;b&gt;inner feelings&lt;/b&gt;&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it works:&lt;/strong&gt; The passage is discussing the cognitive leap of social development. The sentence builds upon the idea that children are learning empathy (understanding other people's feelings). The structure &lt;em&gt;"actions or words don't always reflect their [missing concept]"&lt;/em&gt; requires a concept that is internal and potentially hidden from view. &lt;b&gt;Inner feelings&lt;/b&gt; (or inner emotional states) perfectly contrasts with external manifestations (actions/words). Logically, this completion means: "You can observe someone's actions or words, but those actions don't always reveal their true, internal emotional state."&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Contextual Fit:&lt;/strong&gt; The entire paragraph is about abstract thought and emotional understanding. Using &lt;b&gt;inner feelings&lt;/b&gt; keeps the focus tightly centered on the psychological and emotional development mentioned previously.&lt;/p&gt;
@@ -3060,8 +3023,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As a premium PTE teacher, I will give you a detailed analysis of this Select Missing Word question. In this format, the key is not just knowing vocabulary, but understanding the &lt;strong&gt;context&lt;/strong&gt; and &lt;strong&gt;grammatical function&lt;/strong&gt; required by the surrounding text.&lt;/p&gt;
-&lt;h3&gt;🧠 Contextual Analysis: Why the Answer Works&lt;/h3&gt;
+          <t>&lt;h3&gt;🧠 Contextual Analysis: Why the Answer Works&lt;/h3&gt;
 &lt;p&gt;The entire passage discusses massive, historical movements of people (migrations) that occurred in the 19th century. The sentence leading up to the beep states: "These large movements of people were made possible by the new cheap and fast means of [BEEP]".&lt;/p&gt;
 &lt;p&gt;The text is looking for a general term that describes the physical infrastructure or method used to move huge numbers of people across continents in the past (e.g., steamships, railways). The missing word must be a noun that represents the &lt;strong&gt;means of travel&lt;/strong&gt;.&lt;/p&gt;
 &lt;h3&gt;✅ Correct Choice: Transportation&lt;/h3&gt;
@@ -3171,8 +3133,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;🧠 PTE PTE Listening Strategy: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;This question tests your ability to perform &lt;strong&gt;inference&lt;/strong&gt;. You must not only understand the grammar of the sentence but also deduce the most logical action or concept that completes the idea based on the provided context (the transcript). The surrounding information is key!&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to perform &lt;strong&gt;inference&lt;/strong&gt;. You must not only understand the grammar of the sentence but also deduce the most logical action or concept that completes the idea based on the provided context (the transcript). The surrounding information is key!&lt;/p&gt;
 &lt;h4&gt;🎯 Correct Option Analysis: Follow&lt;/h4&gt;
 &lt;p&gt;The correct answer is &lt;strong&gt;follow&lt;/strong&gt;. This choice is grammatically sound and fits the social context perfectly.&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Contextual Fit:&lt;/strong&gt; The passage discusses the process of domestication, which involves establishing a &lt;em&gt;social structure&lt;/em&gt; and leadership. The sentence sets up a dependency: "If one animal in the group accepts the human as leader..." When a leader is accepted in a social group setting, the natural, expected behavior of the remaining group members is to comply and &lt;strong&gt;follow&lt;/strong&gt; the accepted leader. This action (following) is the core concept of group compliance in anthropology and biology, making it the most contextually accurate conclusion.&lt;/p&gt;
@@ -3215,8 +3176,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;b&gt;🧠 PTE Teacher Analysis: Selecting the Missing Word&lt;/b&gt;&lt;/p&gt;
-&lt;p&gt;This is a classic context-driven vocabulary question. Your primary strategy here must be to listen for the key limiting features described just before the beep, as these features dictate the meaning of the missing action.&lt;/p&gt;
+          <t>&lt;p&gt;This is a classic context-driven vocabulary question. Your primary strategy here must be to listen for the key limiting features described just before the beep, as these features dictate the meaning of the missing action.&lt;/p&gt;
 &lt;h3&gt;🔑 The Core Contextual Clue&lt;/h3&gt;
 &lt;p&gt;The sentence leading up to the beep is: "The robots body and skin stop at his chest though, and he has no robotic legs, so you won't see him [BEEP]."&lt;/p&gt;
 &lt;p&gt;The speaker has explicitly established a physical limitation: the absence of robotic legs. Therefore, the missing phrase must logically relate to a physical action that requires legs or the movement of the lower body. We are looking for a verb phrase that describes movement.&lt;/p&gt;
@@ -3265,8 +3225,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;📚 Detailed PTE Analysis: Select Missing Word (Listening)&lt;/h3&gt;
-&lt;p&gt;&lt;strong&gt;Context Overview:&lt;/strong&gt; The speaker is giving a guided tour of an extreme deep-sea environment, focusing on "black smokers." The passage establishes a sense of wonder, darkness, and the surprising presence of life despite the harsh conditions. The missing phrase must serve as a conclusive statement that summarizes the visual experience described.&lt;/p&gt;
+          <t>&lt;p&gt;&lt;strong&gt;Context Overview:&lt;/strong&gt; The speaker is giving a guided tour of an extreme deep-sea environment, focusing on "black smokers." The passage establishes a sense of wonder, darkness, and the surprising presence of life despite the harsh conditions. The missing phrase must serve as a conclusive statement that summarizes the visual experience described.&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option Analysis: all this fabulous life&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it works:&lt;/strong&gt; This option provides the strongest thematic and contextual conclusion to the monologue. The entire setup—describing the deep, dark, and unusual setting, and mentioning the "remarkable features"—is designed to build suspense and anticipation. The phrase "and it supports all this fabulous life" acts as a perfect summary statement, answering the implicit question: "What is the incredible thing we are looking at?"&lt;/p&gt;
 &lt;ul&gt;
@@ -3318,8 +3277,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As a PTE Academic expert, I can tell you that in Select Missing Word questions, you must analyze not only the grammar but especially the &lt;strong&gt;logic and the overall narrative flow&lt;/strong&gt; of the passage. The context is key here.&lt;/p&gt;
-&lt;h3&gt;✅ Analysis of the Correct Option&lt;/h3&gt;
+          <t>&lt;h3&gt;✅ Analysis of the Correct Option&lt;/h3&gt;
 &lt;h4&gt;&lt;strong&gt;Correct Option: eat plenty of vegetables every day&lt;/strong&gt;&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it is correct:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
@@ -3372,8 +3330,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;🎧 PTE Speaking: Select Missing Word - Detailed Analysis&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This type of question tests not only your listening comprehension but also your understanding of natural English collocations, grammar structures, and conversational context. You must determine which word completes the sentence both grammatically and logically.&lt;/p&gt;
+          <t>&lt;p&gt;This type of question tests not only your listening comprehension but also your understanding of natural English collocations, grammar structures, and conversational context. You must determine which word completes the sentence both grammatically and logically.&lt;/p&gt;
 &lt;h4&gt;✅ Correct Answer Analysis: &lt;strong&gt;wrong&lt;/strong&gt;&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Rationale:&lt;/strong&gt; The correct option is &lt;em&gt;wrong&lt;/em&gt;. The sentence structure is: "I was very sorry to have to tell her that this wasn't [BEEP]."&lt;/p&gt;
 &lt;p&gt;When someone gives an answer that the speaker feels needs correction, the most natural and grammatically sound way to phrase that negative assessment is to say that the answer &lt;strong&gt;wasn't wrong&lt;/strong&gt; (meaning it was incorrect, or factually inaccurate).&lt;/p&gt;
@@ -3424,8 +3381,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;💡 PTE Listening Analysis: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;This question tests your ability to maintain context and grasp the specialized terminology used in academic discourse. The speaker is building a strong analogy to argue for the legitimacy of depression as a medical condition.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to maintain context and grasp the specialized terminology used in academic discourse. The speaker is building a strong analogy to argue for the legitimacy of depression as a medical condition.&lt;/p&gt;
 &lt;h4&gt;🎯 Correct Answer Analysis: disorders&lt;/h4&gt;
 &lt;p&gt;The choice &lt;strong&gt;disorders&lt;/strong&gt; is the only option that maintains the logical, grammatical, and contextual flow of the speaker's argument. &lt;/p&gt;
 &lt;ul&gt;
@@ -3472,8 +3428,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;🌟 PTE Premium Listening Analysis: Select Missing Word&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;In this type of question, &lt;strong&gt;contextual coherence&lt;/strong&gt; is key. You must listen not only for grammar but also for the speaker's main argument or tone. The passage is making a critical point about goal-setting. We must select the phrase that logically concludes the speaker's critique.&lt;/p&gt;
+          <t>&lt;p&gt;In this type of question, &lt;strong&gt;contextual coherence&lt;/strong&gt; is key. You must listen not only for grammar but also for the speaker's main argument or tone. The passage is making a critical point about goal-setting. We must select the phrase that logically concludes the speaker's critique.&lt;/p&gt;
 &lt;h4&gt;✅ Analysis of the Correct Option&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Correct Choice: before you get there&lt;/strong&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Justification:&lt;/strong&gt; The entire passage builds an argument that goal-setting forces us into a state of persistent struggle. The speaker states that when a goal is a long-range goal, the listener "exist[s] in a failure state for a long time until you reach that goal."&lt;/p&gt;
@@ -3519,8 +3474,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As a premium PTE Academic teacher, I will provide a detailed analysis of this Listening Select Missing Word question. This question tests not only your listening comprehension but also your ability to understand the overall structure and key message (the discourse marker) of the text.&lt;/p&gt;
-&lt;h3&gt;🎧 Context Analysis&lt;/h3&gt;
+          <t>&lt;h3&gt;🎧 Context Analysis&lt;/h3&gt;
 &lt;p&gt;The entire passage discusses sleep patterns, emphasizing that sleep occurs in cycles of approximately 90 minutes. The main takeaway message is a practical, actionable piece of advice: to wake up feeling refreshed, you must plan your sleep schedule around these 90-minute cycles. The final sentence acts as a concluding recommendation.&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Concluding sentence:&lt;/strong&gt; "And so if you want to wake up feeling especially alert and refreshed, simply follow [BEEP]"&lt;/p&gt;
 &lt;h3&gt;✅ Analysis of the Correct Option&lt;/h3&gt;
@@ -3575,8 +3529,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Hello! As a PTE Academic teacher, I can tell you that for Select Missing Word questions, you cannot just listen for keywords. You must focus on &lt;strong&gt;coherence&lt;/strong&gt;, &lt;em&gt;grammar&lt;/em&gt;, and the overall scientific/academic context of the passage. The missing phrase must logically complete the idea presented in the preceding clause.&lt;/p&gt;
-&lt;h3&gt;🔍 Detailed Analysis of the Passage and Choices&lt;/h3&gt;
+          <t>&lt;h3&gt;🔍 Detailed Analysis of the Passage and Choices&lt;/h3&gt;
 &lt;p&gt;The final sentence sets up the core mechanism: "they think your brain turns all that stuff you just learned into solid, long term memories by reactivating them and strengthening those [BEEP]." We need a plural noun phrase that represents the fundamental, structural components of learning that require reinforcement to become long-term memories.&lt;/p&gt;
 &lt;h4&gt;✅ The Correct Option: new connections&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it works:&lt;/strong&gt;&lt;/p&gt;
@@ -3628,8 +3581,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Hello! This is a common and often tricky question type because the final word must serve as a perfect summary of the preceding arguments. As your PTE Academic teacher, I will walk you through the logic, grammar, and context to ensure you understand exactly why &lt;strong&gt;change&lt;/strong&gt; is the only correct answer.&lt;/p&gt;
-&lt;h3&gt;🧠 Detailed Analysis of the Missing Word&lt;/h3&gt;
+          <t>&lt;h3&gt;🧠 Detailed Analysis of the Missing Word&lt;/h3&gt;
 &lt;p&gt;The key to answering "Select Missing Word" questions is not just choosing the word that sounds best, but choosing the word that &lt;em&gt;summarizes the central argument&lt;/em&gt; made in the entire passage.&lt;/p&gt;
 &lt;h4&gt;✅ The Correct Option: change&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it works:&lt;/strong&gt;&lt;/p&gt;
@@ -3683,8 +3635,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;🧠 PTE Listening Strategy: Select Missing Word Analysis&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question requires you not just to understand the transcript, but also to track the speaker's main argument and maintain contextual consistency through the final, concluding piece of advice. The speaker establishes a pattern (middle is good, ends are bad) and must finish by applying this pattern.&lt;/p&gt;
+          <t>&lt;p&gt;This question requires you not just to understand the transcript, but also to track the speaker's main argument and maintain contextual consistency through the final, concluding piece of advice. The speaker establishes a pattern (middle is good, ends are bad) and must finish by applying this pattern.&lt;/p&gt;
 &lt;h3&gt;🎯 Analysis of the Correct Choice&lt;/h3&gt;
 &lt;p&gt;&lt;strong&gt;The correct option is: towards the middle of the group&lt;/strong&gt;&lt;/p&gt;
 &lt;h4&gt;Why it Works (Contextual Fit)&lt;/h4&gt;
@@ -3738,8 +3689,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;💡 Expert PTE Analysis: Select Missing Word (Listening)&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question tests your ability to synthesize the main idea and tone of the entire passage, using context and grammar to predict the missing word. The speaker is building a premise: before achieving transformation, there is a necessary preparatory step.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to synthesize the main idea and tone of the entire passage, using context and grammar to predict the missing word. The speaker is building a premise: before achieving transformation, there is a necessary preparatory step.&lt;/p&gt;
 &lt;h3&gt;✅ Correct Option Analysis: &lt;b&gt;listen&lt;/b&gt;&lt;/h3&gt;
 &lt;p&gt;&lt;strong&gt;Contextual Fit:&lt;/strong&gt; This is the strongest choice because "listening" is the central theme of the entire passage. The speaker starts by quoting Parker Palmer, emphasizing the need to &lt;em&gt;listen&lt;/em&gt; to one's life. The entire argument builds on the idea that self-discovery requires deep internal reflection.&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Grammatical Fit:&lt;/strong&gt; The phrase "take the time to &lt;strong&gt;listen&lt;/strong&gt;" is a natural and grammatically perfect infinitive structure, fitting seamlessly into the concluding sentence structure: "We usually wanna get to the transformation and the change right away, but before we can go there, we have to simply take the time to &lt;strong&gt;listen&lt;/strong&gt;."&lt;/p&gt;
@@ -3783,8 +3733,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;🔥 PTE Premium Analysis: Select Missing Word (Listening)&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;This question tests your ability to maintain focus on the speaker's central theme and recognize the number that summarizes their entire argument. The speaker is establishing a clear limit throughout the conversation.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to maintain focus on the speaker's central theme and recognize the number that summarizes their entire argument. The speaker is establishing a clear limit throughout the conversation.&lt;/p&gt;
 &lt;h3&gt;🔑 Analysis of the Correct Option: three&lt;/h3&gt;
 &lt;p&gt;&lt;strong&gt;Context and Logic:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
@@ -3877,8 +3826,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;🔬 PTE Listening Skill Focus: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;This question tests your ability to understand the cohesive flow of an academic discussion and predict the most appropriate vocabulary word to maintain logical and grammatical coherence. Pay close attention to transitional phrases (like "And these differences aren’t just external").&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to understand the cohesive flow of an academic discussion and predict the most appropriate vocabulary word to maintain logical and grammatical coherence. Pay close attention to transitional phrases (like "And these differences aren’t just external").&lt;/p&gt;
 &lt;h4&gt;💡 Contextual Analysis&lt;/h4&gt;
 &lt;p&gt;The speaker has spent the entire passage discussing differences between introverts and extroverts—first behavioral differences (recharging alone vs. with others) and then implying that these differences run deeper than the surface level. The phrase "And these differences aren’t just external" acts as a critical signal, telling the listener that the speaker is about to discuss internal, fundamental, or biological differences. The sentence structure requires an adjective to describe the subject ("The brains... are surprisingly &lt;strong&gt;[ADJECTIVE]&lt;/strong&gt;").&lt;/p&gt;
 &lt;h4&gt;✅ Correct Choice: different&lt;/h4&gt;
@@ -3930,8 +3878,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;📖 PTE Listening: Select Missing Word Analysis&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question tests your ability to maintain &lt;strong&gt;coherence&lt;/strong&gt; and understand the speaker's main concluding point, even when the audio cuts off. In Select Missing Word questions, the missing phrase must logically, grammatically, and contextually complete the preceding thought.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to maintain &lt;strong&gt;coherence&lt;/strong&gt; and understand the speaker's main concluding point, even when the audio cuts off. In Select Missing Word questions, the missing phrase must logically, grammatically, and contextually complete the preceding thought.&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option Analysis: your chance of death&lt;/h4&gt;
 &lt;p&gt;The phrase &lt;em&gt;"your chance of death"&lt;/em&gt; is the perfect contextual fit for the conclusion of the passage. Here is the breakdown:&lt;/p&gt;
 &lt;ul&gt;
@@ -3983,8 +3930,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>&lt;p&gt;🌟 PTE Teacher Analysis: Listening Select Missing Word&lt;/p&gt;
-&lt;p&gt;This question tests not only your listening comprehension but also your ability to maintain contextual flow and understand the core argument being developed by the speaker. The speaker is defining and explaining the concept of &lt;em&gt;decision fatigue&lt;/em&gt;. When you encounter a missing word, you must select the option that logically summarizes the relationship or concept introduced in the passage.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests not only your listening comprehension but also your ability to maintain contextual flow and understand the core argument being developed by the speaker. The speaker is defining and explaining the concept of &lt;em&gt;decision fatigue&lt;/em&gt;. When you encounter a missing word, you must select the option that logically summarizes the relationship or concept introduced in the passage.&lt;/p&gt;
 &lt;h3&gt;✅ Analysis of the Correct Option: constantly making decisions&lt;/h3&gt;
 &lt;p&gt;&lt;strong&gt;The Selection:&lt;/strong&gt; constantly making decisions&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Why it is CORRECT:&lt;/strong&gt;&lt;/p&gt;
@@ -4038,8 +3984,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;🔬 PTE Expert Analysis: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;&lt;strong&gt;Overall Context Summary:&lt;/strong&gt;&lt;/p&gt;
+          <t>&lt;p&gt;&lt;strong&gt;Overall Context Summary:&lt;/strong&gt;&lt;/p&gt;
 &lt;p&gt;The speaker is discussing the fundamental nature of Wikipedia, moving away from the idea of absolute "truth" toward the concept of "what is known"—information determined by consensus. The critical point being made in the final sentences is the uniqueness of Wikipedia's format: every user sees the exact same information.&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;The Gap:&lt;/strong&gt;&lt;/p&gt;
 &lt;p&gt;The sentence preceding the beep states: "One thing that I think is really unique about Wikipedia is there’s only one version for the whole public. There’s no feed that’s curated for you or for me. We all are looking at [BEEP]." The missing phrase must grammatically complete the sentence while reinforcing the idea of &lt;em&gt;shared, singular information&lt;/em&gt;.&lt;/p&gt;
@@ -4084,8 +4029,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;⭐ Premium PTE Listening Analysis: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;This question tests not only your ability to comprehend the spoken English but also your capacity to understand the speaker's core argument and maintain thematic coherence. In Select Missing Word questions, the correct option is almost always the word that summarizes the entire passage's main topic.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests not only your ability to comprehend the spoken English but also your capacity to understand the speaker's core argument and maintain thematic coherence. In Select Missing Word questions, the correct option is almost always the word that summarizes the entire passage's main topic.&lt;/p&gt;
 &lt;h4&gt;💡 Comprehensive Breakdown&lt;/h4&gt;
 &lt;p&gt;The entire passage is built around the concept of the &lt;strong&gt;Attention Economy&lt;/strong&gt;. The speaker establishes that attention is a finite, competitive resource, comparing it to a "zero sum game." The conclusion must logically synthesize this overarching theme.&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option: Attention&lt;/h4&gt;
@@ -4140,8 +4084,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As a premium PTE Academic teacher, I can assure you that for a Select Missing Word question, you must not only understand the vocabulary but also the &lt;strong&gt;narrative flow and logical conclusion&lt;/strong&gt; of the speaker. The key to this question is understanding the final summarizing statement.&lt;/p&gt;
-&lt;h3&gt;🧠 Detailed Analysis of the Passage Context&lt;/h3&gt;
+          <t>&lt;h3&gt;🧠 Detailed Analysis of the Passage Context&lt;/h3&gt;
 &lt;p&gt;The entire passage is structured as an argument: &lt;em&gt;Here is a study... it worked on this specific issue... therefore, this method is highly effective for this condition.&lt;/em&gt; The speaker spends the entire recording detailing how mindfulness-based cognitive therapy (MBCT) helped people suffering from severe depression who had failed other treatments (medication, electric shock).&lt;/p&gt;
 &lt;p&gt;The final sentence, "So mindfulness-based cognitive therapy works very well for [BEEP]," is a concluding statement summarizing the benefit. The missing word must be the core subject of the treatment.&lt;/p&gt;
 &lt;h3&gt;✅ Analysis of the Correct Option: &lt;strong&gt;depression&lt;/strong&gt;&lt;/h3&gt;
@@ -4196,8 +4139,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Hello! As a premium PTE Academic teacher, I can walk you through the logic behind this Select Missing Word question. These questions test not only your listening comprehension but also your ability to predict the speaker's intended meaning and maintain grammatical coherence.&lt;/p&gt;
-&lt;h3&gt;🎧 Analysis of the Passage and Context&lt;/h3&gt;
+          <t>&lt;h3&gt;🎧 Analysis of the Passage and Context&lt;/h3&gt;
 &lt;p&gt;The speaker is discussing the current state of social and political discourse, characterized by accusations of being "triggered." The speaker provides a key example: Google is being sued by two opposing groups—women claiming a hostile climate, and conservatives/white men claiming discrimination. The speaker needs a single phrase to summarize the shared, overarching feeling experienced by &lt;em&gt;all&lt;/em&gt; parties in this polarizing environment.&lt;/p&gt;
 &lt;h3&gt;✅ Analysis of the Correct Option: a victim&lt;/h3&gt;
 &lt;ul&gt;
@@ -4297,8 +4239,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;💡 PTE Teacher's Analysis: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;This question tests your ability to maintain contextual coherence. The passage is building a strong argument: the practice of empathy leads to a measurable positive change (patience). You must select the single word that acts as the direct source or companion to the trait being discussed (patience).&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to maintain contextual coherence. The passage is building a strong argument: the practice of empathy leads to a measurable positive change (patience). You must select the single word that acts as the direct source or companion to the trait being discussed (patience).&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option: empathy&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Contextual Fit:&lt;/strong&gt; This option is the most logical fit because the entire passage has been dedicated to discussing the profound effects of empathy. The speaker notes how understanding others' perspectives (empathy) removes annoyance and builds patience. The final sentence explicitly summarizes this finding: the development of &lt;em&gt;empathy&lt;/em&gt; is what increases &lt;em&gt;patience&lt;/em&gt;. The relationship is causal, making "empathy" the required subject complement.&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Grammatical Fit:&lt;/strong&gt; The phrase "patience associated with [noun]" requires a noun or a conceptual noun. "Empathy" functions perfectly as a conceptual noun, maintaining grammatical balance and narrative flow.&lt;/p&gt;
@@ -4390,8 +4331,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As your PTE Academic teacher, I will provide a detailed breakdown of this Select Missing Word question. The key to these questions is understanding not just the vocabulary, but the overall &lt;em&gt;shift in tone&lt;/em&gt; and the logical relationship between the sentences.&lt;/p&gt;
-&lt;h3&gt;🧐 Overall Context Analysis&lt;/h3&gt;
+          <t>&lt;h3&gt;🧐 Overall Context Analysis&lt;/h3&gt;
 &lt;p&gt;The speaker spends the entire passage warning the listener about the dangers of suppressing emotions (bottling them up). This advice is overwhelmingly negative about repression. When the speaker says, "So instead of repressing how you feel, acknowledge your emotion in a safe environment," they are shifting to provide the &lt;strong&gt;solution&lt;/strong&gt;. Because the solution is presented as advice, it must carry a positive message.&lt;/p&gt;
 &lt;h3&gt;✅ The Correct Answer: beneficial&lt;/h3&gt;
 &lt;ul&gt;
@@ -4494,8 +4434,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;📚 PTE Listening: Select Missing Word Analysis&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question tests not only your listening comprehension but also your ability to maintain &lt;em&gt;contextual coherence&lt;/em&gt; and understand the speaker's logical progression of thought. You must select the phrase that serves as the natural, ultimate conclusion to the argument presented.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests not only your listening comprehension but also your ability to maintain &lt;em&gt;contextual coherence&lt;/em&gt; and understand the speaker's logical progression of thought. You must select the phrase that serves as the natural, ultimate conclusion to the argument presented.&lt;/p&gt;
 &lt;h3&gt;✅ Analysis of the Correct Option: "our real nature"&lt;/h3&gt;
 &lt;p&gt;&lt;strong&gt;Why it is correct:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
@@ -4549,8 +4488,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Hello! As your premium PTE Academic teacher, let’s break down this crucial listening question. In a 'Select Missing Word' question, you must not only understand the general topic (economics/supply curves) but also follow the specific pattern established by the speaker. The speaker is providing evidence, and you must complete the sentence with the conclusion drawn from that evidence.&lt;/p&gt;
-&lt;h3&gt;🔬 Analysis of the Transcript and Context&lt;/h3&gt;
+          <t>&lt;h3&gt;🔬 Analysis of the Transcript and Context&lt;/h3&gt;
 &lt;p&gt;The entire passage is dedicated to explaining the &lt;strong&gt;Law of Supply&lt;/strong&gt;. The speaker establishes a clear, positive correlation (or relationship) between two variables: &lt;em&gt;Price&lt;/em&gt; and &lt;em&gt;Quantity Supplied&lt;/em&gt;.&lt;/p&gt;
 &lt;ul&gt;
     &lt;li&gt;&lt;strong&gt;Initial Statement:&lt;/strong&gt; "A supply curve shows how much... suppliers are willing and able to supply at different prices."&lt;/li&gt;
@@ -4657,8 +4595,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;👩‍🏫 PTE Academic Listening Mastery: Select Missing Word Analysis&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This type of question tests your ability to not only understand vocabulary but also to follow the speaker’s &lt;em&gt;argumentative flow&lt;/em&gt; and thematic consistency. Every word choice must feel like the natural conclusion to the preceding statements. Here is a detailed breakdown of why &lt;strong&gt;humility&lt;/strong&gt; is the only logical and grammatical choice.&lt;/p&gt;
+          <t>&lt;p&gt;This type of question tests your ability to not only understand vocabulary but also to follow the speaker’s &lt;em&gt;argumentative flow&lt;/em&gt; and thematic consistency. Every word choice must feel like the natural conclusion to the preceding statements. Here is a detailed breakdown of why &lt;strong&gt;humility&lt;/strong&gt; is the only logical and grammatical choice.&lt;/p&gt;
 &lt;h4&gt;✅ Analysis of the Correct Option: Humility&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it is correct:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
@@ -4768,8 +4705,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;🎧 PTE Listening Skill Deep Dive: Select Missing Word&lt;/h3&gt;
-&lt;p&gt;This is an excellent example of a context-based inference question. To answer correctly, you cannot just look at the grammar; you must understand the speaker's &lt;strong&gt;main thesis&lt;/strong&gt; and how the final sentence acts as an applied summary of that thesis.&lt;/p&gt;
+          <t>&lt;p&gt;This is an excellent example of a context-based inference question. To answer correctly, you cannot just look at the grammar; you must understand the speaker's &lt;strong&gt;main thesis&lt;/strong&gt; and how the final sentence acts as an applied summary of that thesis.&lt;/p&gt;
 &lt;h4&gt;🎯 Overall Context Analysis&lt;/h4&gt;
 &lt;p&gt;The speaker's entire passage revolves around one central idea: &lt;strong&gt;resisting temptation&lt;/strong&gt;, using the Marshmallow Test as an example. The speaker repeatedly uses language like "minimizing temptations," "resisting temptation," and "the ways that you can actually contractually minimize that temptation."&lt;/p&gt;
 &lt;p&gt;The final sentence, "Oh yeah, if it’s in the back of the cabinet I won’t do it but like actually get rid of the [BEEP]," is the speaker concluding the advice, providing a concrete way to apply the general principle of minimizing temptation.&lt;/p&gt;
@@ -4817,8 +4753,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Hello! As a premium PTE academic teacher, I will provide a detailed breakdown of this Select Missing Word question. This type of question tests not just your vocabulary, but your ability to understand the logical flow and grammatical structure of the entire passage. Focus on the context to make your selection!&lt;/p&gt;
-&lt;h3&gt;🎯 Concept Focus: Contextual Coherence and Grammar&lt;/h3&gt;
+          <t>&lt;h3&gt;🎯 Concept Focus: Contextual Coherence and Grammar&lt;/h3&gt;
 &lt;p&gt;The speaker is discussing the necessity of critical thinking when consuming online information. The overall tone is cautionary, emphasizing that relying on a single source is dangerous. We need a word that completes the thought: "If one source is inadequate, what must you search for?"&lt;/p&gt;
 &lt;h4&gt;✅ Analysis of the Correct Option: &lt;b&gt;validated&lt;/b&gt;&lt;/h4&gt;
 &lt;ul&gt;
@@ -4871,8 +4806,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;🧠 PTE Listening Strategy: Selecting Missing Words&lt;/h3&gt;
-&lt;p&gt;This question tests not only your listening comprehension but also your ability to grasp the precise contextual meaning and grammatical relationship of the missing phrase. In this specific type of PTE question, the entire surrounding context is critical for narrowing down the options.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests not only your listening comprehension but also your ability to grasp the precise contextual meaning and grammatical relationship of the missing phrase. In this specific type of PTE question, the entire surrounding context is critical for narrowing down the options.&lt;/p&gt;
 &lt;h4&gt;🎯 Analysis of the Transcript and Context&lt;/h4&gt;
 &lt;p&gt;The key piece of information in the recording is the phrase: "Most are &lt;strong&gt;self-reported&lt;/strong&gt;, meaning the results are based on questions participants answer about [BEEP]."&lt;/p&gt;
 &lt;p&gt;To understand the missing word, you must focus on the meaning of &lt;em&gt;"self-reported."&lt;/em&gt; This term means that the information (the results) originates directly from the person taking the test (the participants). The structure requires a reflexive pronoun or a phrase that directs the action inward—the participant answers about their own subjective experience.&lt;/p&gt;
@@ -4967,8 +4901,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;h3&gt;🌟 PTE Analysis: Select Missing Word (Listening)&lt;/h3&gt;&lt;/p&gt;
-&lt;p&gt;This question tests your ability to understand the overall context, maintain grammatical parallelism, and select the most logically fitting word to complete a spoken passage. You must determine the concept that completes the philosophical contrast established by the speaker.&lt;/p&gt;
+          <t>&lt;p&gt;This question tests your ability to understand the overall context, maintain grammatical parallelism, and select the most logically fitting word to complete a spoken passage. You must determine the concept that completes the philosophical contrast established by the speaker.&lt;/p&gt;
 &lt;h4&gt;✅ Correct Option Analysis: good&lt;/h4&gt;
 &lt;p&gt;&lt;strong&gt;Why it is correct:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
@@ -5021,8 +4954,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Hello! As a PTE Academic teacher, I will give you a detailed breakdown of this Select Missing Word question. These questions test not only your vocabulary but also your ability to track the speaker's emotional and thematic tone throughout the passage. Pay close attention to the sentiment—it dictates the correct word choice.&lt;/p&gt;
-&lt;h3&gt;📝 Context Analysis: The Tone is Key&lt;/h3&gt;
+          <t>&lt;h3&gt;📝 Context Analysis: The Tone is Key&lt;/h3&gt;
 &lt;p&gt;The entire passage is built around a deeply positive, sensory, and almost meditative experience. The speaker describes the sound of leaves as "fascinating," "soothing," and something that makes it feel like "another realm." When a speaker uses words like &lt;em&gt;soothing&lt;/em&gt; and &lt;em&gt;pure&lt;/em&gt;, the missing word must maintain that same sense of tranquility and positive emotional effect. The final sentence summarizes this positive realization: "I hadn't realized that something so faint, so subtle could be so [BEEP]."&lt;/p&gt;
 &lt;h3&gt;✅ Analysis of the Correct Option: calming&lt;/h3&gt;
 &lt;p&gt;&lt;strong&gt;Why it works:&lt;/strong&gt;&lt;/p&gt;
